--- a/data/美股季營收年增掃描.xlsx
+++ b/data/美股季營收年增掃描.xlsx
@@ -19599,7 +19599,9 @@
       <c r="O11" t="n">
         <v>638</v>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>637.2</v>
+      </c>
       <c r="Q11" t="n">
         <v>7465</v>
       </c>
@@ -19881,7 +19883,9 @@
       <c r="O15" t="n">
         <v>160.6</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Q15" t="n">
         <v>1839.2</v>
       </c>
@@ -20301,7 +20305,9 @@
       <c r="O21" t="n">
         <v>1355.7</v>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1220.1</v>
+      </c>
       <c r="Q21" t="n">
         <v>18218.2</v>
       </c>
@@ -20854,12 +20860,14 @@
         <v>118</v>
       </c>
       <c r="N29" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O29" t="n">
-        <v>139514</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
+        <v>148531</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-2472</v>
+      </c>
       <c r="Q29" t="n">
         <v>916630</v>
       </c>
@@ -22195,7 +22203,9 @@
       <c r="O48" t="n">
         <v>125.9</v>
       </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>109.9</v>
+      </c>
       <c r="Q48" t="n">
         <v>2022</v>
       </c>
@@ -22329,7 +22339,9 @@
       <c r="O50" t="n">
         <v>4646</v>
       </c>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>4621</v>
+      </c>
       <c r="Q50" t="n">
         <v>26828</v>
       </c>
@@ -22737,7 +22749,9 @@
       <c r="O56" t="n">
         <v>5651</v>
       </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>5456</v>
+      </c>
       <c r="Q56" t="n">
         <v>60792</v>
       </c>
@@ -22945,7 +22959,9 @@
       <c r="O59" t="n">
         <v>2510</v>
       </c>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>1604</v>
+      </c>
       <c r="Q59" t="n">
         <v>27983</v>
       </c>
@@ -24201,7 +24217,9 @@
       <c r="O77" t="n">
         <v>1842</v>
       </c>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>-831</v>
+      </c>
       <c r="Q77" t="n">
         <v>29355</v>
       </c>
@@ -24547,7 +24565,9 @@
       <c r="O82" t="n">
         <v>2654</v>
       </c>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>2051</v>
+      </c>
       <c r="Q82" t="n">
         <v>29675</v>
       </c>
@@ -26015,7 +26035,9 @@
       <c r="O103" t="n">
         <v>28.6</v>
       </c>
-      <c r="P103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>27.5</v>
+      </c>
       <c r="Q103" t="n">
         <v>392</v>
       </c>
@@ -26157,7 +26179,9 @@
       <c r="O105" t="n">
         <v>264.2</v>
       </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="n">
+        <v>120.8</v>
+      </c>
       <c r="Q105" t="n">
         <v>1923.9</v>
       </c>
@@ -26361,7 +26385,9 @@
       <c r="O108" t="n">
         <v>4987</v>
       </c>
-      <c r="P108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>3710</v>
+      </c>
       <c r="Q108" t="n">
         <v>75612</v>
       </c>
@@ -26914,13 +26940,13 @@
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
-        <v>1.2</v>
+        <v>0.37</v>
       </c>
       <c r="O116" t="n">
-        <v>81.3</v>
+        <v>24.8</v>
       </c>
       <c r="P116" t="n">
-        <v>78.40000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="Q116" t="n">
         <v>7607.7</v>
@@ -26989,7 +27015,9 @@
       <c r="O117" t="n">
         <v>309.7</v>
       </c>
-      <c r="P117" t="inlineStr"/>
+      <c r="P117" t="n">
+        <v>283.2</v>
+      </c>
       <c r="Q117" t="n">
         <v>5839</v>
       </c>
@@ -27269,7 +27297,9 @@
       <c r="O121" t="n">
         <v>3392</v>
       </c>
-      <c r="P121" t="inlineStr"/>
+      <c r="P121" t="n">
+        <v>1200</v>
+      </c>
       <c r="Q121" t="n">
         <v>45170</v>
       </c>
@@ -27337,7 +27367,9 @@
       <c r="O122" t="n">
         <v>141.1</v>
       </c>
-      <c r="P122" t="inlineStr"/>
+      <c r="P122" t="n">
+        <v>140.5</v>
+      </c>
       <c r="Q122" t="n">
         <v>700.5</v>
       </c>
@@ -27464,13 +27496,13 @@
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="O124" t="n">
-        <v>22</v>
+        <v>26.8</v>
       </c>
       <c r="P124" t="n">
-        <v>19.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q124" t="n">
         <v>2252</v>
@@ -27531,7 +27563,9 @@
       <c r="O125" t="n">
         <v>24</v>
       </c>
-      <c r="P125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>21.4</v>
+      </c>
       <c r="Q125" t="n">
         <v>1604.6</v>
       </c>
@@ -27923,7 +27957,9 @@
       <c r="O131" t="n">
         <v>206</v>
       </c>
-      <c r="P131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>203.7</v>
+      </c>
       <c r="Q131" t="n">
         <v>7839.2</v>
       </c>
@@ -28044,13 +28080,13 @@
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>2.14</v>
+        <v>3.58</v>
       </c>
       <c r="O133" t="n">
-        <v>524.1</v>
+        <v>878.4</v>
       </c>
       <c r="P133" t="n">
-        <v>469.2</v>
+        <v>681</v>
       </c>
       <c r="Q133" t="n">
         <v>76131</v>
@@ -28115,7 +28151,9 @@
       <c r="O134" t="n">
         <v>101.5</v>
       </c>
-      <c r="P134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>96.90000000000001</v>
+      </c>
       <c r="Q134" t="n">
         <v>8141.6</v>
       </c>
@@ -28185,7 +28223,9 @@
       <c r="O135" t="n">
         <v>3716</v>
       </c>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>3469.8</v>
+      </c>
       <c r="Q135" t="n">
         <v>46266</v>
       </c>
@@ -28319,7 +28359,9 @@
       <c r="O137" t="n">
         <v>163.4</v>
       </c>
-      <c r="P137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>163.3</v>
+      </c>
       <c r="Q137" t="n">
         <v>1417.9</v>
       </c>
@@ -28389,7 +28431,9 @@
       <c r="O138" t="n">
         <v>2590.6</v>
       </c>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>2225.8</v>
+      </c>
       <c r="Q138" t="n">
         <v>9883.5</v>
       </c>
@@ -28459,7 +28503,9 @@
       <c r="O139" t="n">
         <v>-1.7</v>
       </c>
-      <c r="P139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>-8.199999999999999</v>
+      </c>
       <c r="Q139" t="n">
         <v>75</v>
       </c>
@@ -28529,7 +28575,9 @@
       <c r="O140" t="n">
         <v>286.1</v>
       </c>
-      <c r="P140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>218.8</v>
+      </c>
       <c r="Q140" t="n">
         <v>1994</v>
       </c>
@@ -28665,7 +28713,9 @@
       <c r="O142" t="n">
         <v>4939.7</v>
       </c>
-      <c r="P142" t="inlineStr"/>
+      <c r="P142" t="n">
+        <v>4771</v>
+      </c>
       <c r="Q142" t="n">
         <v>64484.2</v>
       </c>
@@ -28875,7 +28925,9 @@
       <c r="O145" t="n">
         <v>4371.9</v>
       </c>
-      <c r="P145" t="inlineStr"/>
+      <c r="P145" t="n">
+        <v>4252.4</v>
+      </c>
       <c r="Q145" t="n">
         <v>21656.5</v>
       </c>
@@ -29017,7 +29069,9 @@
       <c r="O147" t="n">
         <v>129.2</v>
       </c>
-      <c r="P147" t="inlineStr"/>
+      <c r="P147" t="n">
+        <v>87.8</v>
+      </c>
       <c r="Q147" t="n">
         <v>1989.8</v>
       </c>
@@ -29223,7 +29277,9 @@
       <c r="O150" t="n">
         <v>726.3</v>
       </c>
-      <c r="P150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>617.5</v>
+      </c>
       <c r="Q150" t="n">
         <v>4219.8</v>
       </c>
@@ -29857,7 +29913,9 @@
       <c r="O159" t="n">
         <v>3186.4</v>
       </c>
-      <c r="P159" t="inlineStr"/>
+      <c r="P159" t="n">
+        <v>2999.1</v>
+      </c>
       <c r="Q159" t="n">
         <v>19850.4</v>
       </c>
@@ -30811,7 +30869,9 @@
       <c r="O173" t="n">
         <v>3030.5</v>
       </c>
-      <c r="P173" t="inlineStr"/>
+      <c r="P173" t="n">
+        <v>2490.7</v>
+      </c>
       <c r="Q173" t="n">
         <v>20111</v>
       </c>
@@ -31767,7 +31827,9 @@
       <c r="O187" t="n">
         <v>0.5</v>
       </c>
-      <c r="P187" t="inlineStr"/>
+      <c r="P187" t="n">
+        <v>-190</v>
+      </c>
       <c r="Q187" t="n">
         <v>1789.7</v>
       </c>
@@ -31903,7 +31965,9 @@
       <c r="O189" t="n">
         <v>29.9</v>
       </c>
-      <c r="P189" t="inlineStr"/>
+      <c r="P189" t="n">
+        <v>-18.9</v>
+      </c>
       <c r="Q189" t="n">
         <v>689.8</v>
       </c>
@@ -32247,7 +32311,9 @@
       <c r="O194" t="n">
         <v>1415.2</v>
       </c>
-      <c r="P194" t="inlineStr"/>
+      <c r="P194" t="n">
+        <v>1412.1</v>
+      </c>
       <c r="Q194" t="n">
         <v>9129.6</v>
       </c>
@@ -32313,7 +32379,9 @@
       <c r="O195" t="n">
         <v>-3742.5</v>
       </c>
-      <c r="P195" t="inlineStr"/>
+      <c r="P195" t="n">
+        <v>-3984.9</v>
+      </c>
       <c r="Q195" t="n">
         <v>53698.3</v>
       </c>
@@ -33365,7 +33433,9 @@
       <c r="O210" t="n">
         <v>3582.6</v>
       </c>
-      <c r="P210" t="inlineStr"/>
+      <c r="P210" t="n">
+        <v>3522.2</v>
+      </c>
       <c r="Q210" t="n">
         <v>44315.6</v>
       </c>
@@ -34328,13 +34398,13 @@
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="O224" t="n">
-        <v>24.6</v>
+        <v>21.6</v>
       </c>
       <c r="P224" t="n">
-        <v>23</v>
+        <v>20.3</v>
       </c>
       <c r="Q224" t="n">
         <v>2200.1</v>
@@ -34547,7 +34617,9 @@
       <c r="O227" t="n">
         <v>102718</v>
       </c>
-      <c r="P227" t="inlineStr"/>
+      <c r="P227" t="n">
+        <v>96676</v>
+      </c>
       <c r="Q227" t="n">
         <v>259474</v>
       </c>
@@ -34689,7 +34761,9 @@
       <c r="O229" t="n">
         <v>12116</v>
       </c>
-      <c r="P229" t="inlineStr"/>
+      <c r="P229" t="n">
+        <v>10773</v>
+      </c>
       <c r="Q229" t="n">
         <v>46934</v>
       </c>
@@ -35093,7 +35167,9 @@
       <c r="O235" t="n">
         <v>81.3</v>
       </c>
-      <c r="P235" t="inlineStr"/>
+      <c r="P235" t="n">
+        <v>74.5</v>
+      </c>
       <c r="Q235" t="n">
         <v>629.5</v>
       </c>
@@ -35215,10 +35291,10 @@
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="n">
-        <v>77.09999999999999</v>
+        <v>166</v>
       </c>
       <c r="P237" t="n">
-        <v>71.7</v>
+        <v>154</v>
       </c>
       <c r="Q237" t="n">
         <v>9466.9</v>
@@ -35285,7 +35361,9 @@
       <c r="O238" t="n">
         <v>686.7</v>
       </c>
-      <c r="P238" t="inlineStr"/>
+      <c r="P238" t="n">
+        <v>571</v>
+      </c>
       <c r="Q238" t="n">
         <v>3376.7</v>
       </c>
@@ -35765,7 +35843,9 @@
       <c r="O245" t="n">
         <v>5008.4</v>
       </c>
-      <c r="P245" t="inlineStr"/>
+      <c r="P245" t="n">
+        <v>4915.4</v>
+      </c>
       <c r="Q245" t="n">
         <v>98133.5</v>
       </c>
@@ -35903,7 +35983,9 @@
       <c r="O247" t="n">
         <v>1413.5</v>
       </c>
-      <c r="P247" t="inlineStr"/>
+      <c r="P247" t="n">
+        <v>1335.7</v>
+      </c>
       <c r="Q247" t="n">
         <v>7339.1</v>
       </c>
@@ -35971,7 +36053,9 @@
       <c r="O248" t="n">
         <v>9601</v>
       </c>
-      <c r="P248" t="inlineStr"/>
+      <c r="P248" t="n">
+        <v>8551</v>
+      </c>
       <c r="Q248" t="n">
         <v>153266</v>
       </c>
@@ -36249,7 +36333,9 @@
       <c r="O252" t="n">
         <v>1850.2</v>
       </c>
-      <c r="P252" t="inlineStr"/>
+      <c r="P252" t="n">
+        <v>1288.5</v>
+      </c>
       <c r="Q252" t="n">
         <v>29099.4</v>
       </c>
@@ -36587,7 +36673,9 @@
       <c r="O257" t="n">
         <v>16.6</v>
       </c>
-      <c r="P257" t="inlineStr"/>
+      <c r="P257" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Q257" t="n">
         <v>458.8</v>
       </c>
@@ -36721,7 +36809,9 @@
       <c r="O259" t="n">
         <v>3911</v>
       </c>
-      <c r="P259" t="inlineStr"/>
+      <c r="P259" t="n">
+        <v>-400</v>
+      </c>
       <c r="Q259" t="n">
         <v>40898</v>
       </c>

--- a/data/美股季營收年增掃描.xlsx
+++ b/data/美股季營收年增掃描.xlsx
@@ -19599,9 +19599,7 @@
       <c r="O11" t="n">
         <v>638</v>
       </c>
-      <c r="P11" t="n">
-        <v>637.2</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
         <v>7465</v>
       </c>
@@ -21759,9 +21757,7 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
-        <v>820.8200000000001</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>2.79</v>
       </c>
@@ -22203,9 +22199,7 @@
       <c r="O48" t="n">
         <v>125.9</v>
       </c>
-      <c r="P48" t="n">
-        <v>109.9</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>2022</v>
       </c>
@@ -22339,9 +22333,7 @@
       <c r="O50" t="n">
         <v>4646</v>
       </c>
-      <c r="P50" t="n">
-        <v>4621</v>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
         <v>26828</v>
       </c>
@@ -26035,9 +26027,7 @@
       <c r="O103" t="n">
         <v>28.6</v>
       </c>
-      <c r="P103" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="n">
         <v>392</v>
       </c>
@@ -26223,9 +26213,7 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="n">
-        <v>345.73</v>
-      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
         <v>1.89</v>
       </c>
@@ -26857,9 +26845,7 @@
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
-        <v>133.05</v>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
         <v>3.77</v>
       </c>
@@ -26923,9 +26909,7 @@
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>2618.1</v>
-      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
         <v>0.95</v>
       </c>
@@ -27367,9 +27351,7 @@
       <c r="O122" t="n">
         <v>141.1</v>
       </c>
-      <c r="P122" t="n">
-        <v>140.5</v>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="n">
         <v>700.5</v>
       </c>
@@ -27479,9 +27461,7 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
-        <v>247.94</v>
-      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
         <v>1.74</v>
       </c>
@@ -28359,9 +28339,7 @@
       <c r="O137" t="n">
         <v>163.4</v>
       </c>
-      <c r="P137" t="n">
-        <v>163.3</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="n">
         <v>1417.9</v>
       </c>
@@ -28503,9 +28481,7 @@
       <c r="O139" t="n">
         <v>-1.7</v>
       </c>
-      <c r="P139" t="n">
-        <v>-8.199999999999999</v>
-      </c>
+      <c r="P139" t="inlineStr"/>
       <c r="Q139" t="n">
         <v>75</v>
       </c>
@@ -29913,9 +29889,7 @@
       <c r="O159" t="n">
         <v>3186.4</v>
       </c>
-      <c r="P159" t="n">
-        <v>2999.1</v>
-      </c>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="n">
         <v>19850.4</v>
       </c>
@@ -30495,9 +30469,7 @@
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" t="n">
-        <v>310.14</v>
-      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>11.4</v>
       </c>
@@ -31664,12 +31636,8 @@
         <v>283.1</v>
       </c>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="n">
-        <v>37.06</v>
-      </c>
-      <c r="H185" t="n">
-        <v>101.47</v>
-      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>2.07</v>
       </c>
@@ -32311,9 +32279,7 @@
       <c r="O194" t="n">
         <v>1415.2</v>
       </c>
-      <c r="P194" t="n">
-        <v>1412.1</v>
-      </c>
+      <c r="P194" t="inlineStr"/>
       <c r="Q194" t="n">
         <v>9129.6</v>
       </c>
@@ -33433,9 +33399,7 @@
       <c r="O210" t="n">
         <v>3582.6</v>
       </c>
-      <c r="P210" t="n">
-        <v>3522.2</v>
-      </c>
+      <c r="P210" t="inlineStr"/>
       <c r="Q210" t="n">
         <v>44315.6</v>
       </c>
@@ -34381,9 +34345,7 @@
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
-      <c r="H224" t="n">
-        <v>623.12</v>
-      </c>
+      <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
         <v>2.77</v>
       </c>
@@ -35843,9 +35805,7 @@
       <c r="O245" t="n">
         <v>5008.4</v>
       </c>
-      <c r="P245" t="n">
-        <v>4915.4</v>
-      </c>
+      <c r="P245" t="inlineStr"/>
       <c r="Q245" t="n">
         <v>98133.5</v>
       </c>
@@ -35983,9 +35943,7 @@
       <c r="O247" t="n">
         <v>1413.5</v>
       </c>
-      <c r="P247" t="n">
-        <v>1335.7</v>
-      </c>
+      <c r="P247" t="inlineStr"/>
       <c r="Q247" t="n">
         <v>7339.1</v>
       </c>
@@ -36053,9 +36011,7 @@
       <c r="O248" t="n">
         <v>9601</v>
       </c>
-      <c r="P248" t="n">
-        <v>8551</v>
-      </c>
+      <c r="P248" t="inlineStr"/>
       <c r="Q248" t="n">
         <v>153266</v>
       </c>
@@ -36308,12 +36264,8 @@
         <v>129.5</v>
       </c>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="n">
-        <v>1091.08</v>
-      </c>
-      <c r="H252" t="n">
-        <v>752.26</v>
-      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
         <v>4.59</v>
       </c>
@@ -36567,27 +36519,29 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>43830</v>
+        <v>2025</v>
       </c>
       <c r="D256" t="n">
         <v>555.9</v>
       </c>
       <c r="E256" t="n">
-        <v>371.9</v>
+        <v>953</v>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="n">
-        <v>1.93</v>
+        <v>14.82</v>
       </c>
       <c r="H256" t="n">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="I256" t="inlineStr"/>
+        <v>5.84</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0.68</v>
+      </c>
       <c r="J256" t="n">
-        <v>37.36</v>
+        <v>-61.93</v>
       </c>
       <c r="K256" t="n">
-        <v>-1.36</v>
+        <v>2.26</v>
       </c>
       <c r="L256" t="n">
         <v>103.32</v>
@@ -36596,13 +36550,13 @@
         <v>108</v>
       </c>
       <c r="N256" t="n">
-        <v>-1.17</v>
+        <v>1.8</v>
       </c>
       <c r="O256" t="n">
-        <v>39.4</v>
+        <v>100</v>
       </c>
       <c r="P256" t="n">
-        <v>28.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q256" t="n">
         <v>2466.2</v>
@@ -36673,9 +36627,7 @@
       <c r="O257" t="n">
         <v>16.6</v>
       </c>
-      <c r="P257" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="P257" t="inlineStr"/>
       <c r="Q257" t="n">
         <v>458.8</v>
       </c>
